--- a/data/trans_orig/IP2003-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2003-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40360</t>
+          <t>40551</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46650</t>
+          <t>46887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40126</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49464</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84810</t>
+          <t>83989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95090</t>
+          <t>94895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>33431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44450</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65184</t>
+          <t>64396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58941</t>
+          <t>58649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73032</t>
+          <t>72762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71477</t>
+          <t>72084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86650</t>
+          <t>86368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135149</t>
+          <t>135937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155883</t>
+          <t>155602</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47884</t>
+          <t>47935</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55852</t>
+          <t>55341</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62828</t>
+          <t>62818</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106649</t>
+          <t>106119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118726</t>
+          <t>118898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31245</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51157</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61538</t>
+          <t>61099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61574</t>
+          <t>61592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71447</t>
+          <t>71399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>115930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129716</t>
+          <t>130334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>24560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33329</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29859</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38380</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57851</t>
+          <t>58083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69765</t>
+          <t>69835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>41200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49863</t>
+          <t>49924</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50168</t>
+          <t>50761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55881</t>
+          <t>55896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94502</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104546</t>
+          <t>104545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35056</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102135</t>
+          <t>102129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113634</t>
+          <t>113756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108584</t>
+          <t>108385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119524</t>
+          <t>119372</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>214496</t>
+          <t>214657</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>230736</t>
+          <t>230138</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>32938</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32692</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40980</t>
+          <t>40163</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61534</t>
+          <t>60852</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117822</t>
+          <t>117937</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132548</t>
+          <t>132397</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>123482</t>
+          <t>123442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137551</t>
+          <t>137797</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>245514</t>
+          <t>246196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>266068</t>
+          <t>266885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>98898</t>
+          <t>98461</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>129850</t>
+          <t>130729</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>84568</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>112638</t>
+          <t>112949</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>190643</t>
+          <t>190555</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>232740</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>515190</t>
+          <t>514311</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>546142</t>
+          <t>546579</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>572252</t>
+          <t>571941</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>600322</t>
+          <t>601015</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1097190</t>
+          <t>1098822</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1139287</t>
+          <t>1139375</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19617</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13960</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27721</t>
+          <t>27707</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>43391</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51088</t>
+          <t>51118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>41182</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87494</t>
+          <t>87508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101255</t>
+          <t>101106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76923</t>
+          <t>77116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87751</t>
+          <t>88212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84534</t>
+          <t>84115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94461</t>
+          <t>94064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165385</t>
+          <t>164811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180266</t>
+          <t>179576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>19744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51795</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>59644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54460</t>
+          <t>54447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62522</t>
+          <t>62498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109172</t>
+          <t>109477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120602</t>
+          <t>120574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25009</t>
+          <t>25399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37613</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48546</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61245</t>
+          <t>61096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62827</t>
+          <t>62932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73567</t>
+          <t>72888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115415</t>
+          <t>115814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131298</t>
+          <t>131972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14553</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26516</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>25790</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35198</t>
+          <t>35324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>40219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60584</t>
+          <t>60485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73274</t>
+          <t>73347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16847</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28247</t>
+          <t>28589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32226</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>41333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49949</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76452</t>
+          <t>76110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89951</t>
+          <t>89985</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19229</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24915</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42865</t>
+          <t>43226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100846</t>
+          <t>100559</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114496</t>
+          <t>114066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111346</t>
+          <t>111261</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>122380</t>
+          <t>122105</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215250</t>
+          <t>214889</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233957</t>
+          <t>233200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26447</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35241</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54758</t>
+          <t>55584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122463</t>
+          <t>122745</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138038</t>
+          <t>138232</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138235</t>
+          <t>138601</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>151506</t>
+          <t>151739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>267572</t>
+          <t>266746</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>287089</t>
+          <t>286759</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>96409</t>
+          <t>96632</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>128679</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>79780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109947</t>
+          <t>109427</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>182712</t>
+          <t>182534</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>225701</t>
+          <t>225112</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>535698</t>
+          <t>534212</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>566482</t>
+          <t>566259</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>593493</t>
+          <t>594013</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>624305</t>
+          <t>623660</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1140630</t>
+          <t>1141219</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1183619</t>
+          <t>1183797</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46864</t>
+          <t>46681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51589</t>
+          <t>51430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58893</t>
+          <t>58897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91603</t>
+          <t>91239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103745</t>
+          <t>104174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>21534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47653</t>
+          <t>46375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77579</t>
+          <t>77497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89553</t>
+          <t>89393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77931</t>
+          <t>77818</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91589</t>
+          <t>92190</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158462</t>
+          <t>159740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177696</t>
+          <t>178038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51108</t>
+          <t>51917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59544</t>
+          <t>59505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57837</t>
+          <t>57930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64500</t>
+          <t>64516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112643</t>
+          <t>112970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123025</t>
+          <t>122967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>26689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>24297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29241</t>
+          <t>28469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47118</t>
+          <t>46398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45762</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59138</t>
+          <t>59226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52479</t>
+          <t>53465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>65372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103406</t>
+          <t>104126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121283</t>
+          <t>122055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34284</t>
+          <t>33518</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30509</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>67847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77427</t>
+          <t>77542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40502</t>
+          <t>40508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48662</t>
+          <t>48691</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43750</t>
+          <t>43716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51556</t>
+          <t>51542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86957</t>
+          <t>86044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98515</t>
+          <t>98206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30730</t>
+          <t>29647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113879</t>
+          <t>114439</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124215</t>
+          <t>124787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115708</t>
+          <t>116284</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126554</t>
+          <t>126871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>232902</t>
+          <t>233985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>248926</t>
+          <t>248749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28791</t>
+          <t>28794</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>46344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123012</t>
+          <t>122796</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>135832</t>
+          <t>135688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133139</t>
+          <t>133669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>145791</t>
+          <t>146608</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>260284</t>
+          <t>261383</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>278936</t>
+          <t>278933</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>73987</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>107974</t>
+          <t>108202</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>160639</t>
+          <t>158663</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>202155</t>
+          <t>200926</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>554621</t>
+          <t>553272</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>584190</t>
+          <t>584568</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>592921</t>
+          <t>592693</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>622828</t>
+          <t>623335</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1157294</t>
+          <t>1158523</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1198810</t>
+          <t>1200786</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>19283</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20993</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>36004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>53578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65142</t>
+          <t>65243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56016</t>
+          <t>55597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113103</t>
+          <t>113865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130626</t>
+          <t>131265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36709</t>
+          <t>37574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91881</t>
+          <t>90756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48753</t>
+          <t>48588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69573</t>
+          <t>67828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151406</t>
+          <t>138536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33730</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88902</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75915</t>
+          <t>76080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100451</t>
+          <t>100124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98873</t>
+          <t>111743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180706</t>
+          <t>182451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49217</t>
+          <t>49131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55039</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>54892</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62789</t>
+          <t>63019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106690</t>
+          <t>107250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116698</t>
+          <t>116905</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>43526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56375</t>
+          <t>58420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54579</t>
+          <t>54548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>65383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29973</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69165</t>
+          <t>68972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88229</t>
+          <t>86184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130136</t>
+          <t>129755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28900</t>
+          <t>28771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>33003</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>38519</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62411</t>
+          <t>62723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70493</t>
+          <t>70575</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>38979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47961</t>
+          <t>48321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53422</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89528</t>
+          <t>89719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96216</t>
+          <t>96189</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29117</t>
+          <t>27352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47873</t>
+          <t>48432</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98310</t>
+          <t>98670</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111826</t>
+          <t>111721</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125740</t>
+          <t>127505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141789</t>
+          <t>142484</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230562</t>
+          <t>230003</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250593</t>
+          <t>250867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11012</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118867</t>
+          <t>118094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126766</t>
+          <t>126545</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>142601</t>
+          <t>143207</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152581</t>
+          <t>152600</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>265793</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>277921</t>
+          <t>277600</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>83378</t>
+          <t>85095</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>192532</t>
+          <t>196712</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>84499</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>138824</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>181128</t>
+          <t>180719</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>298933</t>
+          <t>303305</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>463539</t>
+          <t>459359</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>572693</t>
+          <t>570976</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>608641</t>
+          <t>604857</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>662344</t>
+          <t>662966</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1104603</t>
+          <t>1100231</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1222408</t>
+          <t>1222817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
